--- a/Proyecto Nutricion/ICBF/Valores ingredientes.xlsx
+++ b/Proyecto Nutricion/ICBF/Valores ingredientes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nikol\Documents\Personal\Universidad\Especialización\CTeI\Proyecto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nikol\Documents\GitHub\Proyecto-Nutricion\Proyecto Nutricion\ICBF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{02461006-14D7-4B2B-B6F5-6BD10D4E1673}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16C335E3-8D13-420D-8E84-629BE09CCF22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CEB13A7E-9E83-414B-AA51-FB387A368570}"/>
+    <workbookView xWindow="-135" yWindow="-135" windowWidth="29070" windowHeight="15750" xr2:uid="{CEB13A7E-9E83-414B-AA51-FB387A368570}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -516,12 +516,6 @@
     <t>PAPAYA TAINUNG</t>
   </si>
   <si>
-    <t>PINA GOLD</t>
-  </si>
-  <si>
-    <t>PINA PEROLERA</t>
-  </si>
-  <si>
     <t>TOMATE DE ARBOL</t>
   </si>
   <si>
@@ -601,6 +595,12 @@
   </si>
   <si>
     <t>ZANAHORIA</t>
+  </si>
+  <si>
+    <t>PIÑA GOLD</t>
+  </si>
+  <si>
+    <t>PIÑA PEROLERA</t>
   </si>
 </sst>
 </file>
@@ -644,7 +644,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1059,13 +1059,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B5" s="1">
         <v>10</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D5" s="1">
         <v>1500</v>
@@ -1127,13 +1127,13 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B9" s="1">
         <v>10</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D9" s="1">
         <v>5500</v>
@@ -1161,7 +1161,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B11" s="1">
         <v>10</v>
@@ -1178,13 +1178,13 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B12" s="1">
         <v>10</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D12" s="1">
         <v>1500</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B17" s="1">
         <v>50</v>
@@ -1467,7 +1467,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B29" s="1">
         <v>10</v>
@@ -1671,7 +1671,7 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B41" s="1">
         <v>50</v>
@@ -1688,7 +1688,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B42" s="1">
         <v>50</v>
@@ -1705,13 +1705,13 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B43" s="1">
         <v>25</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D43" s="1">
         <v>3200</v>
@@ -1756,13 +1756,13 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B46" s="1">
         <v>10</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D46" s="1">
         <v>6000</v>
@@ -1790,7 +1790,7 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B48" s="1">
         <v>10</v>
@@ -1994,13 +1994,13 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B60" s="1">
         <v>10</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D60" s="1">
         <v>3000</v>
@@ -2113,7 +2113,7 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B67" s="1">
         <v>50</v>
@@ -2215,7 +2215,7 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B73" s="1">
         <v>50</v>
@@ -2232,7 +2232,7 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B74" s="1">
         <v>50</v>
@@ -2436,7 +2436,7 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B86" s="1">
         <v>10</v>
@@ -2776,7 +2776,7 @@
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B106" s="1">
         <v>50</v>
@@ -3422,7 +3422,7 @@
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>157</v>
+        <v>184</v>
       </c>
       <c r="B144" s="1">
         <v>11</v>
@@ -3439,7 +3439,7 @@
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>158</v>
+        <v>185</v>
       </c>
       <c r="B145" s="1">
         <v>32</v>
@@ -3558,13 +3558,13 @@
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B152" s="1">
         <v>3</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D152" s="1">
         <v>3333</v>
@@ -3575,7 +3575,7 @@
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B153" s="1">
         <v>50</v>
@@ -3592,7 +3592,7 @@
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B154" s="1">
         <v>50</v>
@@ -3677,7 +3677,7 @@
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B159" s="1">
         <v>25</v>
@@ -3762,7 +3762,7 @@
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B164" s="1">
         <v>10</v>
@@ -3779,7 +3779,7 @@
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B165" s="1">
         <v>10</v>
@@ -3796,7 +3796,7 @@
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B166" s="1">
         <v>10</v>
@@ -3864,7 +3864,7 @@
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B170" s="1">
         <v>50</v>
